--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06A629B-E2BB-4155-A44B-6EB9350F63D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC849C5-5729-4A40-B6EC-64190FD22BED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="700">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -2119,6 +2119,12 @@
   </si>
   <si>
     <t>abweichend</t>
+  </si>
+  <si>
+    <t>expectation</t>
+  </si>
+  <si>
+    <t>Erwartung</t>
   </si>
 </sst>
 </file>
@@ -2470,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -5309,6 +5315,14 @@
         <v>659</v>
       </c>
     </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>698</v>
+      </c>
+      <c r="B355" t="s">
+        <v>699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC849C5-5729-4A40-B6EC-64190FD22BED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A710BA2-9CD8-45E1-AAB1-B43A859680FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="740">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -513,9 +513,6 @@
     <t>FACS</t>
   </si>
   <si>
-    <t>Fluorescence-Activated Cell Sorting</t>
-  </si>
-  <si>
     <t>LPS</t>
   </si>
   <si>
@@ -597,9 +594,6 @@
     <t>LoA</t>
   </si>
   <si>
-    <t>level of approvel</t>
-  </si>
-  <si>
     <t>FtO</t>
   </si>
   <si>
@@ -1272,9 +1266,6 @@
     <t>Dosierungslehre</t>
   </si>
   <si>
-    <t xml:space="preserve">mitigation strategy </t>
-  </si>
-  <si>
     <t>Strategie zur Risikominderung</t>
   </si>
   <si>
@@ -2125,6 +2116,135 @@
   </si>
   <si>
     <t>Erwartung</t>
+  </si>
+  <si>
+    <t>level of approval</t>
+  </si>
+  <si>
+    <t>omitted</t>
+  </si>
+  <si>
+    <t>weggelassen</t>
+  </si>
+  <si>
+    <t>Fluorescence Activated Cell Sorting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">risk mitigation strategy </t>
+  </si>
+  <si>
+    <t>pHTE</t>
+  </si>
+  <si>
+    <t>preliminary human therapeutic exposure</t>
+  </si>
+  <si>
+    <t>HDE</t>
+  </si>
+  <si>
+    <t>human dose estimation</t>
+  </si>
+  <si>
+    <t>DDI perpetrator</t>
+  </si>
+  <si>
+    <t>attrition of something</t>
+  </si>
+  <si>
+    <t>Verlust von etwas</t>
+  </si>
+  <si>
+    <t>to reveal something</t>
+  </si>
+  <si>
+    <t>etwas enthüllen</t>
+  </si>
+  <si>
+    <t>withdrawn</t>
+  </si>
+  <si>
+    <t>zurückgezogen</t>
+  </si>
+  <si>
+    <t>Vss</t>
+  </si>
+  <si>
+    <t>volume of distribution</t>
+  </si>
+  <si>
+    <t>Dn</t>
+  </si>
+  <si>
+    <t>dose number</t>
+  </si>
+  <si>
+    <t>FeSSIF</t>
+  </si>
+  <si>
+    <t>FaSSIF</t>
+  </si>
+  <si>
+    <t>seamless</t>
+  </si>
+  <si>
+    <t>nahtlos</t>
+  </si>
+  <si>
+    <t>to deviate from something</t>
+  </si>
+  <si>
+    <t>von etwas abweichen</t>
+  </si>
+  <si>
+    <t>observe</t>
+  </si>
+  <si>
+    <t>beobachten</t>
+  </si>
+  <si>
+    <t>perfused</t>
+  </si>
+  <si>
+    <t>durchblutet</t>
+  </si>
+  <si>
+    <t>disperses</t>
+  </si>
+  <si>
+    <t>verteilt</t>
+  </si>
+  <si>
+    <t>compartment</t>
+  </si>
+  <si>
+    <t>Ablagefach</t>
+  </si>
+  <si>
+    <t>off the cuff</t>
+  </si>
+  <si>
+    <t>aus der Hüfte heraus</t>
+  </si>
+  <si>
+    <t>Verursacher einer Arzneimittelwechselwirkung</t>
+  </si>
+  <si>
+    <t>fasted state simulated intestinal fluid</t>
+  </si>
+  <si>
+    <t>fed state simulated intestinal fluid</t>
+  </si>
+  <si>
+    <t>großer Blutkreislauf (außer Lunge)</t>
+  </si>
+  <si>
+    <t>pulmonary circulation</t>
+  </si>
+  <si>
+    <t>Lungenkreislauf</t>
+  </si>
+  <si>
+    <t>systemic circulation</t>
   </si>
 </sst>
 </file>
@@ -2160,8 +2280,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2476,7 +2600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B375"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -2504,7 +2628,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2528,7 +2652,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2648,7 +2772,7 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -2704,7 +2828,7 @@
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -2728,7 +2852,7 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -2736,7 +2860,7 @@
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -2744,7 +2868,7 @@
         <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -2760,7 +2884,7 @@
         <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -2781,10 +2905,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2821,18 +2945,18 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2840,7 +2964,7 @@
         <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -2880,7 +3004,7 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -2904,7 +3028,7 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -3080,7 +3204,7 @@
         <v>129</v>
       </c>
       <c r="B75" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -3093,10 +3217,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B77" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -3104,7 +3228,7 @@
         <v>132</v>
       </c>
       <c r="B78" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -3120,7 +3244,7 @@
         <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -3144,7 +3268,7 @@
         <v>140</v>
       </c>
       <c r="B83" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -3152,7 +3276,7 @@
         <v>141</v>
       </c>
       <c r="B84" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -3168,7 +3292,7 @@
         <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -3221,10 +3345,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B93" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -3248,535 +3372,535 @@
         <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>162</v>
+        <v>700</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>162</v>
+      </c>
+      <c r="B97" t="s">
         <v>163</v>
-      </c>
-      <c r="B97" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B98" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>165</v>
+      </c>
+      <c r="B99" t="s">
         <v>166</v>
-      </c>
-      <c r="B99" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>167</v>
+      </c>
+      <c r="B100" t="s">
         <v>168</v>
-      </c>
-      <c r="B100" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" t="s">
         <v>170</v>
-      </c>
-      <c r="B101" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>171</v>
+      </c>
+      <c r="B102" t="s">
         <v>172</v>
-      </c>
-      <c r="B102" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B104" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>175</v>
+      </c>
+      <c r="B105" t="s">
         <v>176</v>
-      </c>
-      <c r="B105" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>177</v>
+      </c>
+      <c r="B106" t="s">
         <v>178</v>
-      </c>
-      <c r="B106" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>179</v>
+      </c>
+      <c r="B107" t="s">
         <v>180</v>
-      </c>
-      <c r="B107" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" t="s">
         <v>182</v>
-      </c>
-      <c r="B108" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109" t="s">
         <v>184</v>
-      </c>
-      <c r="B109" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>185</v>
+      </c>
+      <c r="B110" t="s">
         <v>186</v>
-      </c>
-      <c r="B110" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B111" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B112" t="s">
-        <v>190</v>
+        <v>697</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B113" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B114" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B115" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B116" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B117" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B119" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B120" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B122" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B123" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B124" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B126" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B128" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B129" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B130" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B131" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B132" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B133" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B134" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B135" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B136" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B137" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B138" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B139" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B140" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B141" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B142" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B143" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B144" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B145" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B146" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B147" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B149" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B151" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B154" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B155" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B156" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B157" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B158" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B159" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B160" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B161" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B162" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -3789,34 +3913,34 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B164" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B165" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B166" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B167" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -3829,1498 +3953,1658 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B169" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B170" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B171" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B172" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B173" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B174" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B175" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B176" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B178" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B179" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B180" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B181" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B182" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B183" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>343</v>
+      </c>
+      <c r="B184" t="s">
         <v>345</v>
-      </c>
-      <c r="B184" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B185" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B186" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B187" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B188" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B189" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B190" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B191" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B192" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B193" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B194" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B195" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B196" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B197" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B198" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B199" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B200" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B201" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B202" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B203" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B204" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B205" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B206" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B207" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B208" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B209" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B210" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B211" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B212" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>405</v>
+      </c>
+      <c r="B213" t="s">
         <v>407</v>
-      </c>
-      <c r="B213" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>406</v>
+      </c>
+      <c r="B214" t="s">
         <v>408</v>
-      </c>
-      <c r="B214" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B215" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B216" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>415</v>
+        <v>701</v>
       </c>
       <c r="B217" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B218" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B219" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B220" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B221" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B222" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B223" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B224" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B225" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B226" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B227" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B228" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B229" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B230" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B231" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B232" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
+        <v>448</v>
+      </c>
+      <c r="B233" t="s">
         <v>451</v>
-      </c>
-      <c r="B233" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B234" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B235" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B236" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B237" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B238" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B239" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B240" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B241" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B242" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B243" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B244" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B245" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B246" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B247" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B248" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B249" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B250" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B251" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B252" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B253" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B254" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B255" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B256" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B257" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B258" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B259" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B260" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B261" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B262" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B263" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B264" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B265" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B266" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B267" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B268" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B269" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B270" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B271" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B272" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B273" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B274" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B275" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B276" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B277" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B278" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B279" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B280" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B281" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B282" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B283" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B284" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B285" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B286" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B287" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B288" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B289" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B290" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B291" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B292" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B293" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B294" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B295" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B296" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B297" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B298" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B299" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B300" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B301" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B302" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B303" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B304" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B305" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B306" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B307" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B308" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B309" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B310" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B311" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B312" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B313" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B314" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B315" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B316" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B317" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B318" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B319" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B320" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B321" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B322" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B323" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B324" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B325" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B326" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B327" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B328" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B329" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B330" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B331" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B332" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B333" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B334" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B335" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B336" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B337" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B338" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B339" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B340" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B341" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B342" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B343" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B344" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B345" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B346" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B347" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B348" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B349" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B350" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B351" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B352" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B353" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B354" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
+        <v>695</v>
+      </c>
+      <c r="B355" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B356" t="s">
         <v>699</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>702</v>
+      </c>
+      <c r="B357" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>704</v>
+      </c>
+      <c r="B358" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A359" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>707</v>
+      </c>
+      <c r="B360" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>709</v>
+      </c>
+      <c r="B361" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>711</v>
+      </c>
+      <c r="B362" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>713</v>
+      </c>
+      <c r="B363" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>715</v>
+      </c>
+      <c r="B364" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A366" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>719</v>
+      </c>
+      <c r="B367" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>721</v>
+      </c>
+      <c r="B368" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A375" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A710BA2-9CD8-45E1-AAB1-B43A859680FB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973DE637-9495-4C83-899A-1C46B7FB91D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="744">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -2245,6 +2245,18 @@
   </si>
   <si>
     <t>systemic circulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patientenkomfort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient convenience </t>
+  </si>
+  <si>
+    <t>adherence</t>
+  </si>
+  <si>
+    <t>Haftung</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B375"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -5607,6 +5619,22 @@
         <v>736</v>
       </c>
     </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973DE637-9495-4C83-899A-1C46B7FB91D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDADC237-C3F2-414F-ABA8-1C1A45ED36D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="832">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -573,9 +573,6 @@
     <t>nanoDSF</t>
   </si>
   <si>
-    <t>nano Differential Scanning Fluorimetry</t>
-  </si>
-  <si>
     <t>TAA</t>
   </si>
   <si>
@@ -2257,6 +2254,273 @@
   </si>
   <si>
     <t>Haftung</t>
+  </si>
+  <si>
+    <t>tirelessly</t>
+  </si>
+  <si>
+    <t>unermüdlich</t>
+  </si>
+  <si>
+    <t>borderline personality disorder (BPD)</t>
+  </si>
+  <si>
+    <t>Borderline Persönlichkeitsstörung</t>
+  </si>
+  <si>
+    <t>zirkumventrikuläre Organe</t>
+  </si>
+  <si>
+    <t>circumventricular organs (CVOs)</t>
+  </si>
+  <si>
+    <t>Major Depressive Disorder (MDD)</t>
+  </si>
+  <si>
+    <t>schwere depressive Störung</t>
+  </si>
+  <si>
+    <t>BPD</t>
+  </si>
+  <si>
+    <t>borderline personality disorder</t>
+  </si>
+  <si>
+    <t>CVOs</t>
+  </si>
+  <si>
+    <t>circumventricular organs</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>major depressive disorder</t>
+  </si>
+  <si>
+    <t>cognition</t>
+  </si>
+  <si>
+    <t>Bewusstseinsprozesse</t>
+  </si>
+  <si>
+    <t>memory consolidation</t>
+  </si>
+  <si>
+    <t>indication CIAS</t>
+  </si>
+  <si>
+    <t>Cognitive Impairment Associated with Schizophrenia</t>
+  </si>
+  <si>
+    <t>mouse i.p PK</t>
+  </si>
+  <si>
+    <t>mouse intraperitonealen pharmakokinitic</t>
+  </si>
+  <si>
+    <t>intraperitoneal - Injektion durch die Bauchdecke in die Bauchhöhle</t>
+  </si>
+  <si>
+    <t>i.p administration</t>
+  </si>
+  <si>
+    <t>recognition</t>
+  </si>
+  <si>
+    <t>Wiedererkennung</t>
+  </si>
+  <si>
+    <t>extravasation</t>
+  </si>
+  <si>
+    <t>Austritt von Flüssigkeit aus dem Gefäßsystem</t>
+  </si>
+  <si>
+    <t>they do not suffer</t>
+  </si>
+  <si>
+    <t>sie leiden nicht</t>
+  </si>
+  <si>
+    <t>Abuse</t>
+  </si>
+  <si>
+    <t>Missbrauch</t>
+  </si>
+  <si>
+    <t>to administer</t>
+  </si>
+  <si>
+    <t>verabreichen</t>
+  </si>
+  <si>
+    <t>Stabilisierung von Gedächtnisinhalten</t>
+  </si>
+  <si>
+    <t>anesthesialogist</t>
+  </si>
+  <si>
+    <t>Anästhesist</t>
+  </si>
+  <si>
+    <t>to chew</t>
+  </si>
+  <si>
+    <t>kauen</t>
+  </si>
+  <si>
+    <t>You add your name to a list</t>
+  </si>
+  <si>
+    <t>deinen Namen zu einer Liste hinzufügen</t>
+  </si>
+  <si>
+    <t>to abuse</t>
+  </si>
+  <si>
+    <t>missbrauchen</t>
+  </si>
+  <si>
+    <t>deputizing</t>
+  </si>
+  <si>
+    <t>vertreten</t>
+  </si>
+  <si>
+    <t>Cardio Renal Metabolic diseases</t>
+  </si>
+  <si>
+    <t>CRM diseases</t>
+  </si>
+  <si>
+    <t>N&amp;MH diseases</t>
+  </si>
+  <si>
+    <t>I&amp;R diseases</t>
+  </si>
+  <si>
+    <t>neuroscience and mental health diseases</t>
+  </si>
+  <si>
+    <t>inflammation and respiratory diseases</t>
+  </si>
+  <si>
+    <t>Onc</t>
+  </si>
+  <si>
+    <t>oncology</t>
+  </si>
+  <si>
+    <t>Eye health and RBB</t>
+  </si>
+  <si>
+    <t>eye health and research beyond boarder</t>
+  </si>
+  <si>
+    <t>Itinerary</t>
+  </si>
+  <si>
+    <t>Reiseroute</t>
+  </si>
+  <si>
+    <t>grocery store</t>
+  </si>
+  <si>
+    <t>Lebensmittelladen</t>
+  </si>
+  <si>
+    <t>by chance</t>
+  </si>
+  <si>
+    <t>durch Zufall</t>
+  </si>
+  <si>
+    <t>to pass away</t>
+  </si>
+  <si>
+    <t>versterben</t>
+  </si>
+  <si>
+    <t>traffic jam</t>
+  </si>
+  <si>
+    <t>Stau</t>
+  </si>
+  <si>
+    <t>something bothers me</t>
+  </si>
+  <si>
+    <t>etwas stört mich</t>
+  </si>
+  <si>
+    <t>selfish</t>
+  </si>
+  <si>
+    <t>egoistisch</t>
+  </si>
+  <si>
+    <t>to cough</t>
+  </si>
+  <si>
+    <t>husten</t>
+  </si>
+  <si>
+    <t>to sneeze</t>
+  </si>
+  <si>
+    <t>nießen</t>
+  </si>
+  <si>
+    <t>to mitigate something</t>
+  </si>
+  <si>
+    <t>etwas abschwächen</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>Praktikant</t>
+  </si>
+  <si>
+    <t>by tomorrow</t>
+  </si>
+  <si>
+    <t>bis spätestens morgen</t>
+  </si>
+  <si>
+    <t>In urgent matters please contact my colleagues</t>
+  </si>
+  <si>
+    <t>bei dringenden Angelegenheiten wenden Sie sich bitte an meine Kolleginnen und Kollegen</t>
+  </si>
+  <si>
+    <t>degenerative diseases</t>
+  </si>
+  <si>
+    <t>progressiver und irreversibler Funktionsverlust von Zellen oft altersassoziiert</t>
+  </si>
+  <si>
+    <t>FaF</t>
+  </si>
+  <si>
+    <t>fast follower</t>
+  </si>
+  <si>
+    <t>LaF</t>
+  </si>
+  <si>
+    <t>late follower</t>
+  </si>
+  <si>
+    <t>NTC PE</t>
+  </si>
+  <si>
+    <t>new target profile portfolio entry</t>
+  </si>
+  <si>
+    <t>nano Differential Scanning Fluorimetrie</t>
   </si>
 </sst>
 </file>
@@ -2612,11 +2876,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B421"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -2640,7 +2904,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2664,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2784,7 +3048,7 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -2840,7 +3104,7 @@
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -2864,7 +3128,7 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -2872,7 +3136,7 @@
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -2880,7 +3144,7 @@
         <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -2896,7 +3160,7 @@
         <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -2917,10 +3181,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>295</v>
+      </c>
+      <c r="B38" t="s">
         <v>296</v>
-      </c>
-      <c r="B38" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2957,18 +3221,18 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2976,7 +3240,7 @@
         <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -3016,7 +3280,7 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -3040,7 +3304,7 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -3216,7 +3480,7 @@
         <v>129</v>
       </c>
       <c r="B75" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -3229,10 +3493,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>272</v>
+      </c>
+      <c r="B77" t="s">
         <v>273</v>
-      </c>
-      <c r="B77" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -3240,7 +3504,7 @@
         <v>132</v>
       </c>
       <c r="B78" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -3256,7 +3520,7 @@
         <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -3280,7 +3544,7 @@
         <v>140</v>
       </c>
       <c r="B83" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -3288,7 +3552,7 @@
         <v>141</v>
       </c>
       <c r="B84" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -3304,7 +3568,7 @@
         <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -3357,10 +3621,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>397</v>
+      </c>
+      <c r="B93" t="s">
         <v>398</v>
-      </c>
-      <c r="B93" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -3384,7 +3648,7 @@
         <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -3397,7 +3661,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s">
         <v>164</v>
@@ -3437,7 +3701,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B103" t="s">
         <v>173</v>
@@ -3448,7 +3712,7 @@
         <v>174</v>
       </c>
       <c r="B104" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -3480,439 +3744,439 @@
         <v>181</v>
       </c>
       <c r="B108" t="s">
-        <v>182</v>
+        <v>831</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>182</v>
+      </c>
+      <c r="B109" t="s">
         <v>183</v>
-      </c>
-      <c r="B109" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>184</v>
+      </c>
+      <c r="B110" t="s">
         <v>185</v>
-      </c>
-      <c r="B110" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B111" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B112" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>188</v>
+      </c>
+      <c r="B113" t="s">
         <v>189</v>
-      </c>
-      <c r="B113" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>190</v>
+      </c>
+      <c r="B114" t="s">
         <v>191</v>
-      </c>
-      <c r="B114" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>192</v>
+      </c>
+      <c r="B115" t="s">
         <v>193</v>
-      </c>
-      <c r="B115" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B116" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>195</v>
+      </c>
+      <c r="B117" t="s">
         <v>196</v>
-      </c>
-      <c r="B117" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>197</v>
+      </c>
+      <c r="B118" t="s">
         <v>198</v>
-      </c>
-      <c r="B118" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B119" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B120" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>201</v>
+      </c>
+      <c r="B121" t="s">
         <v>202</v>
-      </c>
-      <c r="B121" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B122" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B123" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>205</v>
+      </c>
+      <c r="B124" t="s">
         <v>206</v>
-      </c>
-      <c r="B124" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>207</v>
+      </c>
+      <c r="B125" t="s">
         <v>208</v>
-      </c>
-      <c r="B125" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>209</v>
+      </c>
+      <c r="B126" t="s">
         <v>210</v>
-      </c>
-      <c r="B126" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B128" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>213</v>
+      </c>
+      <c r="B129" t="s">
         <v>214</v>
-      </c>
-      <c r="B129" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>215</v>
+      </c>
+      <c r="B130" t="s">
         <v>216</v>
-      </c>
-      <c r="B130" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>217</v>
+      </c>
+      <c r="B131" t="s">
         <v>218</v>
-      </c>
-      <c r="B131" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>219</v>
+      </c>
+      <c r="B132" t="s">
         <v>220</v>
-      </c>
-      <c r="B132" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>221</v>
+      </c>
+      <c r="B133" t="s">
         <v>222</v>
-      </c>
-      <c r="B133" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>223</v>
+      </c>
+      <c r="B134" t="s">
         <v>224</v>
-      </c>
-      <c r="B134" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>225</v>
+      </c>
+      <c r="B135" t="s">
         <v>226</v>
-      </c>
-      <c r="B135" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B136" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B137" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>229</v>
+      </c>
+      <c r="B138" t="s">
         <v>230</v>
-      </c>
-      <c r="B138" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>231</v>
+      </c>
+      <c r="B139" t="s">
         <v>232</v>
-      </c>
-      <c r="B139" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B140" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>234</v>
+      </c>
+      <c r="B141" t="s">
         <v>235</v>
-      </c>
-      <c r="B141" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>236</v>
+      </c>
+      <c r="B142" t="s">
         <v>237</v>
-      </c>
-      <c r="B142" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>238</v>
+      </c>
+      <c r="B143" t="s">
         <v>239</v>
-      </c>
-      <c r="B143" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>309</v>
+      </c>
+      <c r="B144" t="s">
         <v>310</v>
-      </c>
-      <c r="B144" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>240</v>
+      </c>
+      <c r="B145" t="s">
         <v>241</v>
-      </c>
-      <c r="B145" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>242</v>
+      </c>
+      <c r="B146" t="s">
         <v>243</v>
-      </c>
-      <c r="B146" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>244</v>
+      </c>
+      <c r="B147" t="s">
         <v>245</v>
-      </c>
-      <c r="B147" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>246</v>
+      </c>
+      <c r="B148" t="s">
         <v>247</v>
-      </c>
-      <c r="B148" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>248</v>
+      </c>
+      <c r="B149" t="s">
         <v>249</v>
-      </c>
-      <c r="B149" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>311</v>
+      </c>
+      <c r="B150" t="s">
         <v>312</v>
-      </c>
-      <c r="B150" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>250</v>
+      </c>
+      <c r="B151" t="s">
         <v>251</v>
-      </c>
-      <c r="B151" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>252</v>
+      </c>
+      <c r="B152" t="s">
         <v>253</v>
-      </c>
-      <c r="B152" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>254</v>
+      </c>
+      <c r="B153" t="s">
         <v>255</v>
-      </c>
-      <c r="B153" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>313</v>
+      </c>
+      <c r="B154" t="s">
         <v>314</v>
-      </c>
-      <c r="B154" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>256</v>
+      </c>
+      <c r="B155" t="s">
         <v>257</v>
-      </c>
-      <c r="B155" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>258</v>
+      </c>
+      <c r="B156" t="s">
         <v>259</v>
-      </c>
-      <c r="B156" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>260</v>
+      </c>
+      <c r="B157" t="s">
         <v>261</v>
-      </c>
-      <c r="B157" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>262</v>
+      </c>
+      <c r="B158" t="s">
         <v>263</v>
-      </c>
-      <c r="B158" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>264</v>
+      </c>
+      <c r="B159" t="s">
         <v>265</v>
-      </c>
-      <c r="B159" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>266</v>
+      </c>
+      <c r="B160" t="s">
         <v>267</v>
-      </c>
-      <c r="B160" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>268</v>
+      </c>
+      <c r="B161" t="s">
         <v>269</v>
-      </c>
-      <c r="B161" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>270</v>
+      </c>
+      <c r="B162" t="s">
         <v>271</v>
-      </c>
-      <c r="B162" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -3925,34 +4189,34 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>272</v>
+      </c>
+      <c r="B164" t="s">
         <v>273</v>
-      </c>
-      <c r="B164" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B165" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>276</v>
+      </c>
+      <c r="B166" t="s">
         <v>277</v>
-      </c>
-      <c r="B166" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>278</v>
+      </c>
+      <c r="B167" t="s">
         <v>279</v>
-      </c>
-      <c r="B167" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -3965,1674 +4229,2026 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>280</v>
+      </c>
+      <c r="B169" t="s">
         <v>281</v>
-      </c>
-      <c r="B169" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>282</v>
+      </c>
+      <c r="B170" t="s">
         <v>283</v>
-      </c>
-      <c r="B170" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>284</v>
+      </c>
+      <c r="B171" t="s">
         <v>285</v>
-      </c>
-      <c r="B171" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>286</v>
+      </c>
+      <c r="B172" t="s">
         <v>287</v>
-      </c>
-      <c r="B172" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B173" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>316</v>
+      </c>
+      <c r="B174" t="s">
         <v>317</v>
-      </c>
-      <c r="B174" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>323</v>
+      </c>
+      <c r="B175" t="s">
         <v>324</v>
-      </c>
-      <c r="B175" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>325</v>
+      </c>
+      <c r="B176" t="s">
         <v>326</v>
-      </c>
-      <c r="B176" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>327</v>
+      </c>
+      <c r="B177" t="s">
         <v>328</v>
-      </c>
-      <c r="B177" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>329</v>
+      </c>
+      <c r="B178" t="s">
         <v>330</v>
-      </c>
-      <c r="B178" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>331</v>
+      </c>
+      <c r="B179" t="s">
         <v>332</v>
-      </c>
-      <c r="B179" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>335</v>
+      </c>
+      <c r="B180" t="s">
         <v>336</v>
-      </c>
-      <c r="B180" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>337</v>
+      </c>
+      <c r="B181" t="s">
         <v>338</v>
-      </c>
-      <c r="B181" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B182" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>340</v>
+      </c>
+      <c r="B183" t="s">
         <v>341</v>
-      </c>
-      <c r="B183" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B184" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B185" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B186" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>347</v>
+      </c>
+      <c r="B187" t="s">
         <v>348</v>
-      </c>
-      <c r="B187" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>349</v>
+      </c>
+      <c r="B188" t="s">
         <v>350</v>
-      </c>
-      <c r="B188" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>351</v>
+      </c>
+      <c r="B189" t="s">
         <v>352</v>
-      </c>
-      <c r="B189" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>353</v>
+      </c>
+      <c r="B190" t="s">
         <v>354</v>
-      </c>
-      <c r="B190" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>355</v>
+      </c>
+      <c r="B191" t="s">
         <v>356</v>
-      </c>
-      <c r="B191" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>357</v>
+      </c>
+      <c r="B192" t="s">
         <v>358</v>
-      </c>
-      <c r="B192" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>359</v>
+      </c>
+      <c r="B193" t="s">
         <v>360</v>
-      </c>
-      <c r="B193" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>361</v>
+      </c>
+      <c r="B194" t="s">
         <v>362</v>
-      </c>
-      <c r="B194" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>363</v>
+      </c>
+      <c r="B195" t="s">
         <v>364</v>
-      </c>
-      <c r="B195" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>365</v>
+      </c>
+      <c r="B196" t="s">
         <v>366</v>
-      </c>
-      <c r="B196" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
+        <v>367</v>
+      </c>
+      <c r="B197" t="s">
         <v>368</v>
-      </c>
-      <c r="B197" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>369</v>
+      </c>
+      <c r="B198" t="s">
         <v>370</v>
-      </c>
-      <c r="B198" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
+        <v>371</v>
+      </c>
+      <c r="B199" t="s">
         <v>372</v>
-      </c>
-      <c r="B199" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B200" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B201" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B202" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>377</v>
+      </c>
+      <c r="B203" t="s">
         <v>378</v>
-      </c>
-      <c r="B203" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>379</v>
+      </c>
+      <c r="B204" t="s">
         <v>380</v>
-      </c>
-      <c r="B204" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>381</v>
+      </c>
+      <c r="B205" t="s">
         <v>382</v>
-      </c>
-      <c r="B205" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
+        <v>383</v>
+      </c>
+      <c r="B206" t="s">
         <v>384</v>
-      </c>
-      <c r="B206" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>385</v>
+      </c>
+      <c r="B207" t="s">
         <v>386</v>
-      </c>
-      <c r="B207" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
+        <v>387</v>
+      </c>
+      <c r="B208" t="s">
         <v>388</v>
-      </c>
-      <c r="B208" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
+        <v>389</v>
+      </c>
+      <c r="B209" t="s">
         <v>390</v>
-      </c>
-      <c r="B209" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
+        <v>391</v>
+      </c>
+      <c r="B210" t="s">
         <v>392</v>
-      </c>
-      <c r="B210" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
+        <v>400</v>
+      </c>
+      <c r="B211" t="s">
         <v>401</v>
-      </c>
-      <c r="B211" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>402</v>
+      </c>
+      <c r="B212" t="s">
         <v>403</v>
-      </c>
-      <c r="B212" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B213" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B214" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
+        <v>408</v>
+      </c>
+      <c r="B215" t="s">
         <v>409</v>
-      </c>
-      <c r="B215" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
+        <v>410</v>
+      </c>
+      <c r="B216" t="s">
         <v>411</v>
-      </c>
-      <c r="B216" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B217" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
+        <v>413</v>
+      </c>
+      <c r="B218" t="s">
         <v>414</v>
-      </c>
-      <c r="B218" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>420</v>
+      </c>
+      <c r="B219" t="s">
         <v>421</v>
-      </c>
-      <c r="B219" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
+        <v>422</v>
+      </c>
+      <c r="B220" t="s">
         <v>423</v>
-      </c>
-      <c r="B220" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B221" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>425</v>
+      </c>
+      <c r="B222" t="s">
         <v>426</v>
-      </c>
-      <c r="B222" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>427</v>
+      </c>
+      <c r="B223" t="s">
         <v>428</v>
-      </c>
-      <c r="B223" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
+        <v>429</v>
+      </c>
+      <c r="B224" t="s">
         <v>430</v>
-      </c>
-      <c r="B224" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
+        <v>431</v>
+      </c>
+      <c r="B225" t="s">
         <v>432</v>
-      </c>
-      <c r="B225" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
+        <v>433</v>
+      </c>
+      <c r="B226" t="s">
         <v>434</v>
-      </c>
-      <c r="B226" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
+        <v>436</v>
+      </c>
+      <c r="B227" t="s">
         <v>437</v>
-      </c>
-      <c r="B227" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
+        <v>438</v>
+      </c>
+      <c r="B228" t="s">
         <v>439</v>
-      </c>
-      <c r="B228" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
+        <v>440</v>
+      </c>
+      <c r="B229" t="s">
         <v>441</v>
-      </c>
-      <c r="B229" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
+        <v>442</v>
+      </c>
+      <c r="B230" t="s">
         <v>443</v>
-      </c>
-      <c r="B230" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B231" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
+        <v>445</v>
+      </c>
+      <c r="B232" t="s">
         <v>446</v>
-      </c>
-      <c r="B232" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B233" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
+        <v>448</v>
+      </c>
+      <c r="B234" t="s">
         <v>449</v>
-      </c>
-      <c r="B234" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B235" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>456</v>
+      </c>
+      <c r="B236" t="s">
         <v>457</v>
-      </c>
-      <c r="B236" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
+        <v>458</v>
+      </c>
+      <c r="B237" t="s">
         <v>459</v>
-      </c>
-      <c r="B237" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
+        <v>460</v>
+      </c>
+      <c r="B238" t="s">
         <v>461</v>
-      </c>
-      <c r="B238" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>462</v>
+      </c>
+      <c r="B239" t="s">
         <v>463</v>
-      </c>
-      <c r="B239" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>464</v>
+      </c>
+      <c r="B240" t="s">
         <v>465</v>
-      </c>
-      <c r="B240" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>466</v>
+      </c>
+      <c r="B241" t="s">
         <v>467</v>
-      </c>
-      <c r="B241" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>468</v>
+      </c>
+      <c r="B242" t="s">
         <v>469</v>
-      </c>
-      <c r="B242" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
+        <v>470</v>
+      </c>
+      <c r="B243" t="s">
         <v>471</v>
-      </c>
-      <c r="B243" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
+        <v>472</v>
+      </c>
+      <c r="B244" t="s">
         <v>473</v>
-      </c>
-      <c r="B244" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
+        <v>474</v>
+      </c>
+      <c r="B245" t="s">
         <v>475</v>
-      </c>
-      <c r="B245" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
+        <v>476</v>
+      </c>
+      <c r="B246" t="s">
         <v>477</v>
-      </c>
-      <c r="B246" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
+        <v>478</v>
+      </c>
+      <c r="B247" t="s">
         <v>479</v>
-      </c>
-      <c r="B247" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
+        <v>480</v>
+      </c>
+      <c r="B248" t="s">
         <v>481</v>
-      </c>
-      <c r="B248" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
+        <v>482</v>
+      </c>
+      <c r="B249" t="s">
         <v>483</v>
-      </c>
-      <c r="B249" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
+        <v>486</v>
+      </c>
+      <c r="B250" t="s">
         <v>487</v>
-      </c>
-      <c r="B250" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B251" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B252" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B253" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
+        <v>494</v>
+      </c>
+      <c r="B254" t="s">
         <v>495</v>
-      </c>
-      <c r="B254" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
+        <v>496</v>
+      </c>
+      <c r="B255" t="s">
         <v>497</v>
-      </c>
-      <c r="B255" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B256" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>499</v>
+      </c>
+      <c r="B257" t="s">
         <v>500</v>
-      </c>
-      <c r="B257" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B258" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B259" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
+        <v>503</v>
+      </c>
+      <c r="B260" t="s">
         <v>504</v>
-      </c>
-      <c r="B260" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B261" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B262" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B263" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
+        <v>508</v>
+      </c>
+      <c r="B264" t="s">
         <v>509</v>
-      </c>
-      <c r="B264" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B265" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B266" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B267" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
+        <v>513</v>
+      </c>
+      <c r="B268" t="s">
         <v>514</v>
-      </c>
-      <c r="B268" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B269" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>516</v>
+      </c>
+      <c r="B270" t="s">
         <v>517</v>
-      </c>
-      <c r="B270" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B271" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B272" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
+        <v>520</v>
+      </c>
+      <c r="B273" t="s">
         <v>521</v>
-      </c>
-      <c r="B273" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B274" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B275" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
+        <v>524</v>
+      </c>
+      <c r="B276" t="s">
         <v>525</v>
-      </c>
-      <c r="B276" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
+        <v>526</v>
+      </c>
+      <c r="B277" t="s">
         <v>527</v>
-      </c>
-      <c r="B277" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>528</v>
+      </c>
+      <c r="B278" t="s">
         <v>529</v>
-      </c>
-      <c r="B278" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>530</v>
+      </c>
+      <c r="B279" t="s">
         <v>531</v>
-      </c>
-      <c r="B279" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
+        <v>532</v>
+      </c>
+      <c r="B280" t="s">
         <v>533</v>
-      </c>
-      <c r="B280" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B281" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
+        <v>535</v>
+      </c>
+      <c r="B282" t="s">
         <v>536</v>
-      </c>
-      <c r="B282" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
+        <v>537</v>
+      </c>
+      <c r="B283" t="s">
         <v>538</v>
-      </c>
-      <c r="B283" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B284" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
+        <v>540</v>
+      </c>
+      <c r="B285" t="s">
         <v>541</v>
-      </c>
-      <c r="B285" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
+        <v>542</v>
+      </c>
+      <c r="B286" t="s">
         <v>543</v>
-      </c>
-      <c r="B286" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
+        <v>544</v>
+      </c>
+      <c r="B287" t="s">
         <v>545</v>
-      </c>
-      <c r="B287" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
+        <v>546</v>
+      </c>
+      <c r="B288" t="s">
         <v>547</v>
-      </c>
-      <c r="B288" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B289" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B290" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
+        <v>550</v>
+      </c>
+      <c r="B291" t="s">
         <v>551</v>
-      </c>
-      <c r="B291" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
+        <v>552</v>
+      </c>
+      <c r="B292" t="s">
         <v>553</v>
-      </c>
-      <c r="B292" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
+        <v>554</v>
+      </c>
+      <c r="B293" t="s">
         <v>555</v>
-      </c>
-      <c r="B293" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B294" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B295" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
+        <v>558</v>
+      </c>
+      <c r="B296" t="s">
         <v>559</v>
-      </c>
-      <c r="B296" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
+        <v>560</v>
+      </c>
+      <c r="B297" t="s">
         <v>561</v>
-      </c>
-      <c r="B297" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
+        <v>562</v>
+      </c>
+      <c r="B298" t="s">
         <v>563</v>
-      </c>
-      <c r="B298" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B299" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
+        <v>565</v>
+      </c>
+      <c r="B300" t="s">
         <v>566</v>
-      </c>
-      <c r="B300" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
+        <v>567</v>
+      </c>
+      <c r="B301" t="s">
         <v>568</v>
-      </c>
-      <c r="B301" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>569</v>
+      </c>
+      <c r="B302" t="s">
         <v>570</v>
-      </c>
-      <c r="B302" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
+        <v>571</v>
+      </c>
+      <c r="B303" t="s">
         <v>572</v>
-      </c>
-      <c r="B303" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>573</v>
+      </c>
+      <c r="B304" t="s">
         <v>574</v>
-      </c>
-      <c r="B304" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B305" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
+        <v>576</v>
+      </c>
+      <c r="B306" t="s">
         <v>577</v>
-      </c>
-      <c r="B306" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B307" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
+        <v>579</v>
+      </c>
+      <c r="B308" t="s">
         <v>580</v>
-      </c>
-      <c r="B308" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B309" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
+        <v>582</v>
+      </c>
+      <c r="B310" t="s">
         <v>583</v>
-      </c>
-      <c r="B310" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
+        <v>584</v>
+      </c>
+      <c r="B311" t="s">
         <v>585</v>
-      </c>
-      <c r="B311" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B312" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
+        <v>587</v>
+      </c>
+      <c r="B313" t="s">
         <v>588</v>
-      </c>
-      <c r="B313" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B314" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
+        <v>590</v>
+      </c>
+      <c r="B315" t="s">
         <v>591</v>
-      </c>
-      <c r="B315" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B316" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
+        <v>593</v>
+      </c>
+      <c r="B317" t="s">
         <v>594</v>
-      </c>
-      <c r="B317" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
+        <v>595</v>
+      </c>
+      <c r="B318" t="s">
         <v>596</v>
-      </c>
-      <c r="B318" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
+        <v>597</v>
+      </c>
+      <c r="B319" t="s">
         <v>598</v>
-      </c>
-      <c r="B319" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
+        <v>599</v>
+      </c>
+      <c r="B320" t="s">
         <v>600</v>
-      </c>
-      <c r="B320" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B321" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
+        <v>602</v>
+      </c>
+      <c r="B322" t="s">
         <v>603</v>
-      </c>
-      <c r="B322" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
+        <v>604</v>
+      </c>
+      <c r="B323" t="s">
         <v>605</v>
-      </c>
-      <c r="B323" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
+        <v>606</v>
+      </c>
+      <c r="B324" t="s">
         <v>607</v>
-      </c>
-      <c r="B324" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B325" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B326" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
+        <v>610</v>
+      </c>
+      <c r="B327" t="s">
         <v>611</v>
-      </c>
-      <c r="B327" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B328" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
+        <v>613</v>
+      </c>
+      <c r="B329" t="s">
         <v>614</v>
-      </c>
-      <c r="B329" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B330" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
+        <v>616</v>
+      </c>
+      <c r="B331" t="s">
         <v>617</v>
-      </c>
-      <c r="B331" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B332" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
+        <v>619</v>
+      </c>
+      <c r="B333" t="s">
         <v>620</v>
-      </c>
-      <c r="B333" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
+        <v>621</v>
+      </c>
+      <c r="B334" t="s">
         <v>622</v>
-      </c>
-      <c r="B334" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
+        <v>623</v>
+      </c>
+      <c r="B335" t="s">
         <v>624</v>
-      </c>
-      <c r="B335" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B336" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B337" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>627</v>
+      </c>
+      <c r="B338" t="s">
         <v>628</v>
-      </c>
-      <c r="B338" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
+        <v>629</v>
+      </c>
+      <c r="B339" t="s">
         <v>630</v>
-      </c>
-      <c r="B339" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
+        <v>631</v>
+      </c>
+      <c r="B340" t="s">
         <v>632</v>
-      </c>
-      <c r="B340" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
+        <v>633</v>
+      </c>
+      <c r="B341" t="s">
         <v>634</v>
-      </c>
-      <c r="B341" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
+        <v>635</v>
+      </c>
+      <c r="B342" t="s">
         <v>636</v>
-      </c>
-      <c r="B342" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B343" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
+        <v>638</v>
+      </c>
+      <c r="B344" t="s">
         <v>639</v>
-      </c>
-      <c r="B344" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
+        <v>640</v>
+      </c>
+      <c r="B345" t="s">
         <v>641</v>
-      </c>
-      <c r="B345" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
+        <v>642</v>
+      </c>
+      <c r="B346" t="s">
         <v>643</v>
-      </c>
-      <c r="B346" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B347" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
+        <v>645</v>
+      </c>
+      <c r="B348" t="s">
         <v>646</v>
-      </c>
-      <c r="B348" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B349" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
+        <v>649</v>
+      </c>
+      <c r="B351" t="s">
         <v>650</v>
-      </c>
-      <c r="B351" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
+        <v>651</v>
+      </c>
+      <c r="B352" t="s">
         <v>652</v>
-      </c>
-      <c r="B352" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B353" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
+        <v>654</v>
+      </c>
+      <c r="B354" t="s">
         <v>655</v>
-      </c>
-      <c r="B354" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
+        <v>694</v>
+      </c>
+      <c r="B355" t="s">
         <v>695</v>
-      </c>
-      <c r="B355" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B356" t="s">
         <v>698</v>
-      </c>
-      <c r="B356" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
+        <v>701</v>
+      </c>
+      <c r="B357" t="s">
         <v>702</v>
-      </c>
-      <c r="B357" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
+        <v>703</v>
+      </c>
+      <c r="B358" t="s">
         <v>704</v>
-      </c>
-      <c r="B358" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="359" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
+        <v>706</v>
+      </c>
+      <c r="B360" t="s">
         <v>707</v>
-      </c>
-      <c r="B360" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
+        <v>708</v>
+      </c>
+      <c r="B361" t="s">
         <v>709</v>
-      </c>
-      <c r="B361" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
+        <v>710</v>
+      </c>
+      <c r="B362" t="s">
         <v>711</v>
-      </c>
-      <c r="B362" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
+        <v>712</v>
+      </c>
+      <c r="B363" t="s">
         <v>713</v>
-      </c>
-      <c r="B363" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
+        <v>714</v>
+      </c>
+      <c r="B364" t="s">
         <v>715</v>
-      </c>
-      <c r="B364" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="365" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="366" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
+        <v>718</v>
+      </c>
+      <c r="B367" t="s">
         <v>719</v>
-      </c>
-      <c r="B367" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
+        <v>720</v>
+      </c>
+      <c r="B368" t="s">
         <v>721</v>
-      </c>
-      <c r="B368" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B370" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B371" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B372" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B373" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B374" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="375" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B377" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="B377" s="2" t="s">
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="2" t="s">
         <v>743</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>751</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>753</v>
+      </c>
+      <c r="B383" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>755</v>
+      </c>
+      <c r="B384" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>757</v>
+      </c>
+      <c r="B385" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>759</v>
+      </c>
+      <c r="B386" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>760</v>
+      </c>
+      <c r="B387" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>762</v>
+      </c>
+      <c r="B388" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>765</v>
+      </c>
+      <c r="B389" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>766</v>
+      </c>
+      <c r="B390" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>768</v>
+      </c>
+      <c r="B391" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>770</v>
+      </c>
+      <c r="B392" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>772</v>
+      </c>
+      <c r="B393" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>774</v>
+      </c>
+      <c r="B394" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>777</v>
+      </c>
+      <c r="B395" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>779</v>
+      </c>
+      <c r="B396" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>781</v>
+      </c>
+      <c r="B397" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>783</v>
+      </c>
+      <c r="B398" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>785</v>
+      </c>
+      <c r="B399" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>788</v>
+      </c>
+      <c r="B400" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>789</v>
+      </c>
+      <c r="B401" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>790</v>
+      </c>
+      <c r="B402" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>793</v>
+      </c>
+      <c r="B403" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>795</v>
+      </c>
+      <c r="B404" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>797</v>
+      </c>
+      <c r="B405" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>799</v>
+      </c>
+      <c r="B406" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>801</v>
+      </c>
+      <c r="B407" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>803</v>
+      </c>
+      <c r="B408" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>805</v>
+      </c>
+      <c r="B409" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>807</v>
+      </c>
+      <c r="B410" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>809</v>
+      </c>
+      <c r="B411" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>811</v>
+      </c>
+      <c r="B412" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>813</v>
+      </c>
+      <c r="B413" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>815</v>
+      </c>
+      <c r="B414" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>817</v>
+      </c>
+      <c r="B415" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>819</v>
+      </c>
+      <c r="B416" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>821</v>
+      </c>
+      <c r="B417" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>823</v>
+      </c>
+      <c r="B418" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>825</v>
+      </c>
+      <c r="B419" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>827</v>
+      </c>
+      <c r="B420" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>829</v>
+      </c>
+      <c r="B421" t="s">
+        <v>830</v>
       </c>
     </row>
   </sheetData>

--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDADC237-C3F2-414F-ABA8-1C1A45ED36D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F699518A-466D-42DA-9B36-65F134EBDFDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="858">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -2521,6 +2521,84 @@
   </si>
   <si>
     <t>nano Differential Scanning Fluorimetrie</t>
+  </si>
+  <si>
+    <t>cardiovascular diseases</t>
+  </si>
+  <si>
+    <t>Herz Kreislauf Erkrankungen</t>
+  </si>
+  <si>
+    <t>curtailed</t>
+  </si>
+  <si>
+    <t>eingeschränkt</t>
+  </si>
+  <si>
+    <t>genetic predisposition</t>
+  </si>
+  <si>
+    <t>genetische Veranlagung</t>
+  </si>
+  <si>
+    <t>in turn markedly</t>
+  </si>
+  <si>
+    <t>erhöht wiederum deutlich</t>
+  </si>
+  <si>
+    <t>disability</t>
+  </si>
+  <si>
+    <t>Behinderung</t>
+  </si>
+  <si>
+    <t>stroke</t>
+  </si>
+  <si>
+    <t>Schlaganfall</t>
+  </si>
+  <si>
+    <t>heart attack</t>
+  </si>
+  <si>
+    <t>Herzinfarkt</t>
+  </si>
+  <si>
+    <t>limbs</t>
+  </si>
+  <si>
+    <t>Gliedmaßen</t>
+  </si>
+  <si>
+    <t>among partners</t>
+  </si>
+  <si>
+    <t>unter Partnern</t>
+  </si>
+  <si>
+    <t>hypertension</t>
+  </si>
+  <si>
+    <t>Bluthochdruck</t>
+  </si>
+  <si>
+    <t>anemia</t>
+  </si>
+  <si>
+    <t>Blutarmut</t>
+  </si>
+  <si>
+    <t>lag time</t>
+  </si>
+  <si>
+    <t>Zeitverzögerung</t>
+  </si>
+  <si>
+    <t>disruption</t>
+  </si>
+  <si>
+    <t>Störung</t>
   </si>
 </sst>
 </file>
@@ -2876,7 +2954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.77734375" bestFit="1" customWidth="1"/>
@@ -6251,6 +6329,110 @@
         <v>830</v>
       </c>
     </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>832</v>
+      </c>
+      <c r="B422" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>834</v>
+      </c>
+      <c r="B423" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>836</v>
+      </c>
+      <c r="B424" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>838</v>
+      </c>
+      <c r="B425" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>840</v>
+      </c>
+      <c r="B426" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>842</v>
+      </c>
+      <c r="B427" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>844</v>
+      </c>
+      <c r="B428" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>846</v>
+      </c>
+      <c r="B429" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>848</v>
+      </c>
+      <c r="B430" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>850</v>
+      </c>
+      <c r="B431" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>852</v>
+      </c>
+      <c r="B432" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>854</v>
+      </c>
+      <c r="B433" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>856</v>
+      </c>
+      <c r="B434" t="s">
+        <v>857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/sample_memory.xlsx
+++ b/sample_memory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bixenmann\Documents\Eigene Dokumente\SynologyDrive\VSC_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F699518A-466D-42DA-9B36-65F134EBDFDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB6E497-19E6-4E2F-A5D6-04E581956D59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{95876C56-AE7E-409F-849F-6EA48A653E4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="876">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -2517,12 +2517,6 @@
     <t>NTC PE</t>
   </si>
   <si>
-    <t>new target profile portfolio entry</t>
-  </si>
-  <si>
-    <t>nano Differential Scanning Fluorimetrie</t>
-  </si>
-  <si>
     <t>cardiovascular diseases</t>
   </si>
   <si>
@@ -2599,6 +2593,66 @@
   </si>
   <si>
     <t>Störung</t>
+  </si>
+  <si>
+    <t>new target concept portfolio entry</t>
+  </si>
+  <si>
+    <t>ultimate MPO Endpoint</t>
+  </si>
+  <si>
+    <t>nano Differential Scanning Fluorometrie</t>
+  </si>
+  <si>
+    <t>endgültiges multi parameter Optimierungs Zielprofil</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>alcohol use disorder</t>
+  </si>
+  <si>
+    <t>CUD</t>
+  </si>
+  <si>
+    <t>cocaine use disorder</t>
+  </si>
+  <si>
+    <t>Reha</t>
+  </si>
+  <si>
+    <t>tremor</t>
+  </si>
+  <si>
+    <t>zittern</t>
+  </si>
+  <si>
+    <t>Gleichgewichtsstörungen</t>
+  </si>
+  <si>
+    <t>postural instability</t>
+  </si>
+  <si>
+    <t>vielversprechend</t>
+  </si>
+  <si>
+    <t>favorable</t>
+  </si>
+  <si>
+    <t>inflection point</t>
+  </si>
+  <si>
+    <t>Wendepunkt</t>
+  </si>
+  <si>
+    <t>Rückfallprävention</t>
+  </si>
+  <si>
+    <t>relapse prevention</t>
+  </si>
+  <si>
+    <t>rehab</t>
   </si>
 </sst>
 </file>
@@ -2954,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33951E89-29DC-4789-ADCB-5AEF5E1F2D6E}">
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.77734375" bestFit="1" customWidth="1"/>
@@ -3822,7 +3876,7 @@
         <v>181</v>
       </c>
       <c r="B108" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -6326,111 +6380,191 @@
         <v>829</v>
       </c>
       <c r="B421" t="s">
-        <v>830</v>
+        <v>856</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B422" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B423" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B424" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B425" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B426" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B427" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B428" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B429" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B430" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B431" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B432" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B433" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B434" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>221</v>
+      </c>
+      <c r="B435" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
         <v>857</v>
+      </c>
+      <c r="B436" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>875</v>
+      </c>
+      <c r="B437" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>865</v>
+      </c>
+      <c r="B438" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>868</v>
+      </c>
+      <c r="B439" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>870</v>
+      </c>
+      <c r="B440" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>871</v>
+      </c>
+      <c r="B441" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>874</v>
+      </c>
+      <c r="B442" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>860</v>
+      </c>
+      <c r="B443" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>862</v>
+      </c>
+      <c r="B444" t="s">
+        <v>863</v>
       </c>
     </row>
   </sheetData>
